--- a/federated-learning-master/results/metrics_comparison_20250408_133650.xlsx
+++ b/federated-learning-master/results/metrics_comparison_20250408_133650.xlsx
@@ -1,37 +1,92 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\西安交通大学学习资料\大四\b毕业设计\main_project\federated-learning-master\results\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19050" windowHeight="6860"/>
   </bookViews>
   <sheets>
-    <sheet name="Metrics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Metrics" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>mse</t>
+  </si>
+  <si>
+    <t>mae</t>
+  </si>
+  <si>
+    <t>mre</t>
+  </si>
+  <si>
+    <t>cos_sim</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>TMC</t>
+  </si>
+  <si>
+    <t>GMC</t>
+  </si>
+  <si>
+    <t>GTMC</t>
+  </si>
+  <si>
+    <t>Baseline</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Train</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,94 +101,2031 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t>Non-iid Mnist FL</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>项目耗时分布</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-706D-4CBB-B405-7141357B549B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-706D-4CBB-B405-7141357B549B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:solidFill>
+                <a:sysClr val="window" lastClr="FFFFFF"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="25000"/>
+                    <a:lumOff val="75000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-CN"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <a:prstGeom prst="wedgeRectCallout">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                </c15:spPr>
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Metrics!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>MC</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>TMC</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>GMC</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>GTMC</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Baseline</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Train</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Metrics!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>450.22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>58.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>448.01</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>65.150000000000006</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>951.78</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>497.79</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-706D-4CBB-B405-7141357B549B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="0"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>Non-iid Cifar FL</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="zh-CN" sz="1400" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>项目耗时分布</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-CN" altLang="zh-CN" sz="1400">
+              <a:effectLst/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-B402-4357-833C-AF93BC3EAA4F}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.2049335863377609"/>
+                  <c:y val="-6.4814814814814894E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-B402-4357-833C-AF93BC3EAA4F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:solidFill>
+                <a:sysClr val="window" lastClr="FFFFFF"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="25000"/>
+                    <a:lumOff val="75000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-CN"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <a:prstGeom prst="wedgeRectCallout">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                </c15:spPr>
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Metrics!$A$11:$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>MC</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>TMC</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>GMC</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>GTMC</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Baseline</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Train</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Metrics!$B$11:$B$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>612.79999999999995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>80.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>619.66</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>80.56</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1092.71</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1225.0899999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B402-4357-833C-AF93BC3EAA4F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="0"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>603250</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="图表 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>844550</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>577850</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="图表 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -420,143 +2412,185 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="8"/>
-    <col customWidth="1" max="2" min="2" width="19"/>
-    <col customWidth="1" max="3" min="3" width="24"/>
-    <col customWidth="1" max="4" min="4" width="23"/>
-    <col customWidth="1" max="5" min="5" width="23"/>
-    <col customWidth="1" max="6" min="6" width="20"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="5" width="23" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>mse</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>mae</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mre</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>cos_sim</t>
-        </is>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MC</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>450.2229166030884</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1.5155320107034e-08</v>
-      </c>
-      <c r="D2" t="n">
-        <v>9.325661726656623e-05</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.0002840987589494366</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.9999999783524041</v>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>450.22</v>
+      </c>
+      <c r="C2">
+        <v>1.5155320107034E-8</v>
+      </c>
+      <c r="D2">
+        <v>9.3256617266566233E-5</v>
+      </c>
+      <c r="E2">
+        <v>2.840987589494366E-4</v>
+      </c>
+      <c r="F2">
+        <v>0.99999997835240406</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TMC</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>58.50432848930359</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.007893210861065404</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.06755082416920269</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.1395576381528399</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.9885468046377111</v>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>58.5</v>
+      </c>
+      <c r="C3">
+        <v>7.8932108610654042E-3</v>
+      </c>
+      <c r="D3">
+        <v>6.7550824169202689E-2</v>
+      </c>
+      <c r="E3">
+        <v>0.13955763815283989</v>
+      </c>
+      <c r="F3">
+        <v>0.98854680463771105</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>GMC</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>448.0142939090729</v>
-      </c>
-      <c r="C4" t="n">
-        <v>9.749945760972587e-09</v>
-      </c>
-      <c r="D4" t="n">
-        <v>8.075342738234556e-05</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.0002170968346397021</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9999999858847752</v>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>448.01</v>
+      </c>
+      <c r="C4">
+        <v>9.7499457609725869E-9</v>
+      </c>
+      <c r="D4">
+        <v>8.0753427382345555E-5</v>
+      </c>
+      <c r="E4">
+        <v>2.1709683463970209E-4</v>
+      </c>
+      <c r="F4">
+        <v>0.99999998588477523</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>GTMC</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>65.14899682998657</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.009284206746750194</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.06562189366226456</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.1336944729658587</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9865859615298507</v>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>65.150000000000006</v>
+      </c>
+      <c r="C5">
+        <v>9.2842067467501944E-3</v>
+      </c>
+      <c r="D5">
+        <v>6.5621893662264563E-2</v>
+      </c>
+      <c r="E5">
+        <v>0.13369447296585871</v>
+      </c>
+      <c r="F5">
+        <v>0.98658596152985067</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>951.78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>497.79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11">
+        <v>612.79999999999995</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12">
+        <v>80.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13">
+        <v>619.66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14">
+        <v>80.56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15">
+        <v>1092.71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16">
+        <v>1225.0899999999999</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>